--- a/templates/INFRA GER ADV M - template.xlsx
+++ b/templates/INFRA GER ADV M - template.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$11</definedName>
@@ -1393,96 +1393,96 @@
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B19" s="33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C19" s="34" t="n">
-        <v>1.01145015</v>
+        <v>1.01486927</v>
       </c>
       <c r="D19" s="35" t="n">
-        <v>0.0003488783573175613</v>
+        <v>0.001493335032242582</v>
       </c>
       <c r="E19" s="35" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>0.6429013381497377</v>
+        <v>2.751867722367057</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C20" s="38" t="n">
-        <v>1.0110974</v>
+        <v>1.01335599</v>
       </c>
       <c r="D20" s="39" t="n">
-        <v>0.000681278551122988</v>
+        <v>0.0006522493939096208</v>
       </c>
       <c r="E20" s="39" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>1.255437269131043</v>
+        <v>1.201943311634433</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B21" s="37" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C21" s="38" t="n">
-        <v>1.01040903</v>
+        <v>1.01269546</v>
       </c>
       <c r="D21" s="39" t="n">
-        <v>0.0004339729726621222</v>
+        <v>0.0007747218924309962</v>
       </c>
       <c r="E21" s="39" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>0.7997108418833234</v>
+        <v>1.427631525117576</v>
       </c>
     </row>
     <row r="22" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B22" s="37" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C22" s="38" t="n">
-        <v>1.00997073</v>
+        <v>1.01191151</v>
       </c>
       <c r="D22" s="39" t="n">
-        <v>0.000220401486636046</v>
+        <v>-0.0008662615114689576</v>
       </c>
       <c r="E22" s="39" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>0.4061484689906644</v>
+        <v>-1.596317665541169</v>
       </c>
     </row>
     <row r="23" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B23" s="37" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C23" s="38" t="n">
-        <v>1.00974818</v>
+        <v>1.01278885</v>
       </c>
       <c r="D23" s="39" t="n">
-        <v>0.0004021926240025397</v>
+        <v>-0.0005106156158554143</v>
       </c>
       <c r="E23" s="39" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>0.7411470810435726</v>
+        <v>-0.9409453347511334</v>
       </c>
     </row>
     <row r="24" ht="15.95" customHeight="1">
@@ -1522,18 +1522,18 @@
     <row r="26" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B26" s="53" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C26" s="53" t="inlineStr"/>
       <c r="D26" s="39" t="n">
-        <v>0.008727684764312515</v>
+        <v>0.001309200363548646</v>
       </c>
       <c r="E26" s="39" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F26" s="40" t="n">
-        <v>0.8325268376668098</v>
+        <v>0.3440893956172711</v>
       </c>
       <c r="G26" s="54" t="n"/>
     </row>
@@ -1545,13 +1545,13 @@
       </c>
       <c r="C27" s="53" t="inlineStr"/>
       <c r="D27" s="39" t="n">
-        <v>0.01002572082617603</v>
+        <v>0.007788167376508781</v>
       </c>
       <c r="E27" s="39" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F27" s="40" t="n">
-        <v>0.8644461214623561</v>
+        <v>0.6766188210588517</v>
       </c>
       <c r="G27" s="54" t="n"/>
     </row>
@@ -1563,13 +1563,13 @@
       </c>
       <c r="C28" s="41" t="inlineStr"/>
       <c r="D28" s="39" t="n">
-        <v>0.01145014999999994</v>
+        <v>0.01486926999999993</v>
       </c>
       <c r="E28" s="39" t="n">
-        <v>0.01327189162505582</v>
+        <v>0.01878398381837676</v>
       </c>
       <c r="F28" s="40" t="n">
-        <v>0.8627368519483204</v>
+        <v>0.7915929945304265</v>
       </c>
       <c r="G28" s="42" t="n"/>
     </row>
@@ -1581,13 +1581,13 @@
       </c>
       <c r="C29" s="41" t="inlineStr"/>
       <c r="D29" s="39" t="n">
-        <v>0.01145014999999994</v>
+        <v>0.01486926999999993</v>
       </c>
       <c r="E29" s="39" t="n">
-        <v>0.01327189162505582</v>
+        <v>0.01878398381837676</v>
       </c>
       <c r="F29" s="40" t="n">
-        <v>0.8627368519483204</v>
+        <v>0.7915929945304265</v>
       </c>
       <c r="G29" s="42" t="n"/>
     </row>
@@ -1615,7 +1615,7 @@
       <c r="C32" s="12" t="n"/>
       <c r="D32" s="12" t="n"/>
       <c r="E32" s="43" t="n">
-        <v>211568598.74</v>
+        <v>285189972.96</v>
       </c>
       <c r="F32" s="27" t="n"/>
       <c r="G32" s="3" t="n"/>
@@ -1630,7 +1630,7 @@
       <c r="C33" s="12" t="n"/>
       <c r="D33" s="12" t="n"/>
       <c r="E33" s="43" t="n">
-        <v>141353178.4564</v>
+        <v>172396597.5705714</v>
       </c>
       <c r="F33" s="27" t="n"/>
       <c r="G33" s="3" t="n"/>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D35" s="18" t="n"/>
